--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755621354_individual_h_4.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755621354_individual_h_4.xlsx
@@ -658,7 +658,7 @@
         <v>0.02650770384816609</v>
       </c>
       <c r="C2" t="n">
-        <v>24851088</v>
+        <v>6212772</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>24851088</v>
+        <v>6212772</v>
       </c>
       <c r="K2" t="n">
-        <v>18445872</v>
+        <v>4344634</v>
       </c>
       <c r="L2" t="n">
-        <v>11347751</v>
+        <v>2503846</v>
       </c>
       <c r="M2" t="n">
-        <v>3020876</v>
+        <v>628661</v>
       </c>
       <c r="N2" t="n">
-        <v>187539</v>
+        <v>32114</v>
       </c>
       <c r="O2" t="n">
-        <v>1770073</v>
+        <v>384494</v>
       </c>
       <c r="P2" t="n">
-        <v>697787</v>
+        <v>157985</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.999979555606842</v>
+        <v>0.9999515414237976</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9402310252189636</v>
+        <v>0.8858264088630676</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8691810369491577</v>
+        <v>0.7662560939788818</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8224962949752808</v>
+        <v>0.687294065952301</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6853193044662476</v>
+        <v>0.4724105894565582</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8680628538131714</v>
+        <v>0.7542529106140137</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9058616161346436</v>
+        <v>0.8200920820236206</v>
       </c>
       <c r="X2" t="n">
-        <v>24851088</v>
+        <v>6212772</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>24851088</v>
+        <v>6212772</v>
       </c>
       <c r="AF2" t="n">
-        <v>17857588</v>
+        <v>4226955</v>
       </c>
       <c r="AG2" t="n">
-        <v>10387905</v>
+        <v>2305814</v>
       </c>
       <c r="AH2" t="n">
-        <v>2705736</v>
+        <v>572610</v>
       </c>
       <c r="AI2" t="n">
-        <v>170728</v>
+        <v>30514</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1614925</v>
+        <v>353874</v>
       </c>
       <c r="AK2" t="n">
-        <v>656266</v>
+        <v>148866</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9041380882263184</v>
+        <v>0.8560509085655212</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.8105198740959167</v>
+        <v>0.7196477651596069</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.7304050922393799</v>
+        <v>0.6182972192764282</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.4829482436180115</v>
+        <v>0.3452669084072113</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.7946620583534241</v>
+        <v>0.6965283155441284</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.848928689956665</v>
+        <v>0.7702767848968506</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.006837913715981852</v>
       </c>
       <c r="C3" t="n">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="D3" t="n">
-        <v>18445872</v>
+        <v>4344634</v>
       </c>
       <c r="E3" t="n">
-        <v>1187729</v>
+        <v>539758</v>
       </c>
       <c r="F3" t="n">
-        <v>36161</v>
+        <v>17532</v>
       </c>
       <c r="G3" t="n">
-        <v>8019</v>
+        <v>3539</v>
       </c>
       <c r="H3" t="n">
-        <v>638</v>
+        <v>419</v>
       </c>
       <c r="I3" t="n">
-        <v>172</v>
+        <v>86</v>
       </c>
       <c r="J3" t="n">
-        <v>39430004</v>
+        <v>9857327</v>
       </c>
       <c r="K3" t="n">
-        <v>43430356</v>
+        <v>10604399</v>
       </c>
       <c r="L3" t="n">
-        <v>49699373</v>
+        <v>12076524</v>
       </c>
       <c r="M3" t="n">
-        <v>59914932</v>
+        <v>14854143</v>
       </c>
       <c r="N3" t="n">
-        <v>63841159</v>
+        <v>15945844</v>
       </c>
       <c r="O3" t="n">
-        <v>61977269</v>
+        <v>15435873</v>
       </c>
       <c r="P3" t="n">
-        <v>63435893</v>
+        <v>15842396</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9373536109924316</v>
+        <v>0.885571300983429</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8814269304275513</v>
+        <v>0.7751638889312744</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8132154941558838</v>
+        <v>0.6758139133453369</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5292807817459106</v>
+        <v>0.3620885908603668</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8696877956390381</v>
+        <v>0.7550156712532043</v>
       </c>
       <c r="W3" t="n">
-        <v>0.9024757146835327</v>
+        <v>0.8171102404594421</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>17857588</v>
+        <v>4226955</v>
       </c>
       <c r="Z3" t="n">
-        <v>1701428</v>
+        <v>634345</v>
       </c>
       <c r="AA3" t="n">
-        <v>74417</v>
+        <v>29509</v>
       </c>
       <c r="AB3" t="n">
-        <v>43535</v>
+        <v>14127</v>
       </c>
       <c r="AC3" t="n">
-        <v>1450</v>
+        <v>987</v>
       </c>
       <c r="AD3" t="n">
-        <v>251</v>
+        <v>101</v>
       </c>
       <c r="AE3" t="n">
-        <v>39430512</v>
+        <v>9857628</v>
       </c>
       <c r="AF3" t="n">
-        <v>42709567</v>
+        <v>10453593</v>
       </c>
       <c r="AG3" t="n">
-        <v>48978861</v>
+        <v>11942041</v>
       </c>
       <c r="AH3" t="n">
-        <v>59568174</v>
+        <v>14786674</v>
       </c>
       <c r="AI3" t="n">
-        <v>63744488</v>
+        <v>15923845</v>
       </c>
       <c r="AJ3" t="n">
-        <v>61829012</v>
+        <v>15406967</v>
       </c>
       <c r="AK3" t="n">
-        <v>63391622</v>
+        <v>15832657</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9074591398239136</v>
+        <v>0.8615846633911133</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.8068717122077942</v>
+        <v>0.7138553261756897</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.7283802628517151</v>
+        <v>0.6155587434768677</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.4818360507488251</v>
+        <v>0.3440484404563904</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.7934591174125671</v>
+        <v>0.6948884129524231</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.8487749695777893</v>
+        <v>0.7699460983276367</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.066113121495729</v>
       </c>
       <c r="C4" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D4" t="n">
-        <v>1109188</v>
+        <v>532236</v>
       </c>
       <c r="E4" t="n">
-        <v>11347751</v>
+        <v>2503846</v>
       </c>
       <c r="F4" t="n">
-        <v>383737</v>
+        <v>173924</v>
       </c>
       <c r="G4" t="n">
-        <v>11749</v>
+        <v>5892</v>
       </c>
       <c r="H4" t="n">
-        <v>20294</v>
+        <v>13065</v>
       </c>
       <c r="I4" t="n">
-        <v>1544</v>
+        <v>1100</v>
       </c>
       <c r="J4" t="n">
-        <v>508</v>
+        <v>301</v>
       </c>
       <c r="K4" t="n">
-        <v>1172575</v>
+        <v>559977</v>
       </c>
       <c r="L4" t="n">
-        <v>1707931</v>
+        <v>763790</v>
       </c>
       <c r="M4" t="n">
-        <v>651938</v>
+        <v>286029</v>
       </c>
       <c r="N4" t="n">
-        <v>86113</v>
+        <v>35865</v>
       </c>
       <c r="O4" t="n">
-        <v>269034</v>
+        <v>125274</v>
       </c>
       <c r="P4" t="n">
-        <v>72515</v>
+        <v>34658</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999898076057434</v>
+        <v>0.9999757409095764</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9387900829315186</v>
+        <v>0.8856988549232483</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8752611875534058</v>
+        <v>0.7706842422485352</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8178296089172363</v>
+        <v>0.6815056800842285</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5972769856452942</v>
+        <v>0.409957230091095</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8688745498657227</v>
+        <v>0.7546341419219971</v>
       </c>
       <c r="W4" t="n">
-        <v>0.904165506362915</v>
+        <v>0.8185984492301941</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1793382</v>
+        <v>674862</v>
       </c>
       <c r="Z4" t="n">
-        <v>10387905</v>
+        <v>2305814</v>
       </c>
       <c r="AA4" t="n">
-        <v>608586</v>
+        <v>212641</v>
       </c>
       <c r="AB4" t="n">
-        <v>39858</v>
+        <v>13807</v>
       </c>
       <c r="AC4" t="n">
-        <v>40802</v>
+        <v>20791</v>
       </c>
       <c r="AD4" t="n">
-        <v>3763</v>
+        <v>2171</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1893364</v>
+        <v>710783</v>
       </c>
       <c r="AG4" t="n">
-        <v>2428443</v>
+        <v>898273</v>
       </c>
       <c r="AH4" t="n">
-        <v>998696</v>
+        <v>353498</v>
       </c>
       <c r="AI4" t="n">
-        <v>182784</v>
+        <v>57864</v>
       </c>
       <c r="AJ4" t="n">
-        <v>417291</v>
+        <v>154180</v>
       </c>
       <c r="AK4" t="n">
-        <v>116786</v>
+        <v>44397</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9057955741882324</v>
+        <v>0.8588088154792786</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.808691680431366</v>
+        <v>0.71673983335495</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.7293912768363953</v>
+        <v>0.6169249415397644</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.4823915064334869</v>
+        <v>0.3446566164493561</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.7940601110458374</v>
+        <v>0.695707380771637</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.8488518595695496</v>
+        <v>0.7701113820075989</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="D5" t="n">
-        <v>36866</v>
+        <v>16675</v>
       </c>
       <c r="E5" t="n">
-        <v>462030</v>
+        <v>195660</v>
       </c>
       <c r="F5" t="n">
-        <v>3020876</v>
+        <v>628661</v>
       </c>
       <c r="G5" t="n">
-        <v>35994</v>
+        <v>14478</v>
       </c>
       <c r="H5" t="n">
-        <v>150585</v>
+        <v>69451</v>
       </c>
       <c r="I5" t="n">
-        <v>8305</v>
+        <v>5252</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1232797</v>
+        <v>561390</v>
       </c>
       <c r="L5" t="n">
-        <v>1526545</v>
+        <v>726240</v>
       </c>
       <c r="M5" t="n">
-        <v>693854</v>
+        <v>301567</v>
       </c>
       <c r="N5" t="n">
-        <v>166789</v>
+        <v>56577</v>
       </c>
       <c r="O5" t="n">
-        <v>265224</v>
+        <v>124759</v>
       </c>
       <c r="P5" t="n">
-        <v>75405</v>
+        <v>35361</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999920725822449</v>
+        <v>0.9999812841415405</v>
       </c>
       <c r="R5" t="n">
-        <v>0.962580680847168</v>
+        <v>0.9302216172218323</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9496827125549316</v>
+        <v>0.9072811007499695</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9790641069412231</v>
+        <v>0.9634361267089844</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9960657358169556</v>
+        <v>0.9942476749420166</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9916887879371643</v>
+        <v>0.9844413995742798</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9976989030838013</v>
+        <v>0.9956429600715637</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>59870</v>
+        <v>23010</v>
       </c>
       <c r="Z5" t="n">
-        <v>643769</v>
+        <v>226432</v>
       </c>
       <c r="AA5" t="n">
-        <v>2705736</v>
+        <v>572610</v>
       </c>
       <c r="AB5" t="n">
-        <v>55681</v>
+        <v>16757</v>
       </c>
       <c r="AC5" t="n">
-        <v>232966</v>
+        <v>83037</v>
       </c>
       <c r="AD5" t="n">
-        <v>16708</v>
+        <v>8382</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1821081</v>
+        <v>679069</v>
       </c>
       <c r="AG5" t="n">
-        <v>2486391</v>
+        <v>924272</v>
       </c>
       <c r="AH5" t="n">
-        <v>1008994</v>
+        <v>357618</v>
       </c>
       <c r="AI5" t="n">
-        <v>183600</v>
+        <v>58177</v>
       </c>
       <c r="AJ5" t="n">
-        <v>420372</v>
+        <v>155379</v>
       </c>
       <c r="AK5" t="n">
-        <v>116926</v>
+        <v>44480</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9422160387039185</v>
+        <v>0.9135147929191589</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9235421419143677</v>
+        <v>0.8865899443626404</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9687672853469849</v>
+        <v>0.9557499289512634</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9943003058433533</v>
+        <v>0.9927791953086853</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9869688749313354</v>
+        <v>0.9807373285293579</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9963642358779907</v>
+        <v>0.9944695234298706</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>214</v>
+        <v>119</v>
       </c>
       <c r="D6" t="n">
-        <v>26351</v>
+        <v>10980</v>
       </c>
       <c r="E6" t="n">
-        <v>38533</v>
+        <v>15127</v>
       </c>
       <c r="F6" t="n">
-        <v>70105</v>
+        <v>18123</v>
       </c>
       <c r="G6" t="n">
-        <v>187539</v>
+        <v>32114</v>
       </c>
       <c r="H6" t="n">
-        <v>28705</v>
+        <v>10870</v>
       </c>
       <c r="I6" t="n">
-        <v>2881</v>
+        <v>1358</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>39538</v>
+        <v>12528</v>
       </c>
       <c r="Z6" t="n">
-        <v>40699</v>
+        <v>14491</v>
       </c>
       <c r="AA6" t="n">
-        <v>60750</v>
+        <v>18090</v>
       </c>
       <c r="AB6" t="n">
-        <v>170728</v>
+        <v>30514</v>
       </c>
       <c r="AC6" t="n">
-        <v>38246</v>
+        <v>11381</v>
       </c>
       <c r="AD6" t="n">
-        <v>4367</v>
+        <v>1687</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="D7" t="n">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="E7" t="n">
-        <v>18679</v>
+        <v>12634</v>
       </c>
       <c r="F7" t="n">
-        <v>157882</v>
+        <v>73941</v>
       </c>
       <c r="G7" t="n">
-        <v>28930</v>
+        <v>11245</v>
       </c>
       <c r="H7" t="n">
-        <v>1770073</v>
+        <v>384494</v>
       </c>
       <c r="I7" t="n">
-        <v>59613</v>
+        <v>26862</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>396</v>
+        <v>328</v>
       </c>
       <c r="Z7" t="n">
-        <v>40532</v>
+        <v>21886</v>
       </c>
       <c r="AA7" t="n">
-        <v>246662</v>
+        <v>89027</v>
       </c>
       <c r="AB7" t="n">
-        <v>41085</v>
+        <v>12082</v>
       </c>
       <c r="AC7" t="n">
-        <v>1614925</v>
+        <v>353874</v>
       </c>
       <c r="AD7" t="n">
-        <v>91697</v>
+        <v>32056</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="D8" t="n">
-        <v>94</v>
+        <v>38</v>
       </c>
       <c r="E8" t="n">
-        <v>960</v>
+        <v>611</v>
       </c>
       <c r="F8" t="n">
-        <v>4053</v>
+        <v>2509</v>
       </c>
       <c r="G8" t="n">
-        <v>1421</v>
+        <v>711</v>
       </c>
       <c r="H8" t="n">
-        <v>68812</v>
+        <v>31469</v>
       </c>
       <c r="I8" t="n">
-        <v>697787</v>
+        <v>157985</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>178</v>
+        <v>55</v>
       </c>
       <c r="Z8" t="n">
-        <v>2015</v>
+        <v>1119</v>
       </c>
       <c r="AA8" t="n">
-        <v>8281</v>
+        <v>4231</v>
       </c>
       <c r="AB8" t="n">
-        <v>2625</v>
+        <v>1091</v>
       </c>
       <c r="AC8" t="n">
-        <v>103827</v>
+        <v>37984</v>
       </c>
       <c r="AD8" t="n">
-        <v>656266</v>
+        <v>148866</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
